--- a/stories/arbres/ATOM-VIV.ANI.001-04.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rosa marche avec papa. Ils suivent le chemin du pré. Un chien arrive. Le chien aboie. Ouaf ouaf. Papa dit : le chien aboie. C'est son cri. Un chat saute près d'une botte. Le chat miaule. Miaou. Une vache mange l'herbe. La vache meugle. Meuh. Un coq est sur la clôture. Le coq chante. Cocorico. Un mouton s'approche. Le mouton bêle. Bêê. Un canard nage dans la mare. Le canard cancane. Papa dit : chaque animal a un cri. Rosa nomme l'animal. Elle dit le cri.</t>
+          <t>Rosa marche avec papa. Ils suivent le chemin du pré. Un chien arrive. Le chien aboie. Ouaf ouaf. Le chien aboie. C'est son cri. Un chat saute près d'une botte. Le chat miaule. Miaou. Une vache mange l'herbe. La vache meugle. Meuh. Un coq est sur la clôture. Le coq chante. Cocorico. Un mouton s'approche. Le mouton bêle. Bêê. Un canard nage dans la mare. Le canard cancane. Chaque animal a un cri. Rosa nomme l'animal. Elle dit le cri.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Rosa marche avec papa. Ils suivent le chemin du pré. Un chien arrive. Le chien aboie. Ouaf ouaf.
+papa|Le chien aboie. C'est son cri.
+narrateur|Un chat saute près d'une botte. Le chat miaule. Miaou. Une vache mange l'herbe. La vache meugle. Meuh. Un coq est sur la clôture. Le coq chante. Cocorico. Un mouton s'approche. Le mouton bêle. Bêê. Un canard nage dans la mare. Le canard cancane.
+papa|Chaque animal a un cri.
+narrateur|Rosa nomme l'animal. Elle dit le cri.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le chien fait ouaf. Quel est son cri ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Rosa a nommé l'animal. Elle a dit le cri. Chien, chat, vache, coq, mouton, canard.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Rosa tient la main de papa. Le pré sent l'herbe.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-04.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Rosa nomme l'animal. Elle dit le cri.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Le chien fait ouaf. Quel est son cri ?</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -1672,6 +1687,11 @@
           <t>narrateur|Rosa a nommé l'animal. Elle a dit le cri. Chien, chat, vache, coq, mouton, canard.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1859,7 @@
           <t>narrateur|Rosa tient la main de papa. Le pré sent l'herbe.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2027,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2070,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2285,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.001-04.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rosa nomme les cris au pré</t>
+          <t>La pomme du cheval</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut donner une pomme au cheval. La pomme de l'arbre est trop haute. Ils en trouvent une à terre. Papa la donne.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Rosa marche avec papa. Ils suivent le chemin du pré. Un chien arrive. Le chien aboie. Ouaf ouaf. Le chien aboie. C'est son cri. Un chat saute près d'une botte. Le chat miaule. Miaou. Une vache mange l'herbe. La vache meugle. Meuh. Un coq est sur la clôture. Le coq chante. Cocorico. Un mouton s'approche. Le mouton bêle. Bêê. Un canard nage dans la mare. Le canard cancane. Chaque animal a un cri. Rosa nomme l'animal. Elle dit le cri.</t>
+          <t>Le pommier du pré penche vers la clôture. Une pomme verte brille tout en haut. Des mouches tournent au-dessus de l'herbe. Ça sent le sucré et le crottin chaud. Tu vois le pommier, Mila ? Oui. Je veux le cheval. Le cheval du pré ? Lui donner une pomme. En ce moment, Mila lève le nez. La pomme du haut est trop loin. Je n'arrive pas. Elle est trop haute. Un hennissement arrive du pré. Hiii, long et doux. Le cheval ! Tu as entendu ? Il appelle. Le cheval hennit. Mila marche le long de la clôture. L'herbe racle ses mollets. Une pomme brune dort dans l'herbe. Une à terre ! On la ramasse ? Oui. Mila se baisse. La pomme est froide et un peu molle. Elle la tend vers le pré. On ne donne pas tout seuls. Je la donne, d'accord ? D'accord. Papa prend la pomme dans sa main. Le cheval s'approche de la clôture. Son museau est velours et tiède. Il souffle. Hiii. Une mouche se pose sur l'encolure. Il attend la pomme. Oui. Les naseaux du cheval s'ouvrent tout grand. La clôture tremble un peu sous le poil. Il est tout près. On reste de ce côté. Mila sent le sucré de la pomme froide.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Rosa marche avec papa. Ils suivent le chemin du pré. Un chien arrive. Le chien aboie. Ouaf ouaf. Papa dit : le chien aboie. C'est son cri. Un chat saute près d'une botte. Le chat miaule. Miaou. Une vache mange l'herbe. La vache meugle. Meuh. Un coq est sur la clôture. Le coq chante. Cocorico. Un mouton s'approche. Le mouton bêle. Bêê. Un canard nage dans la mare. Le canard cancane. Papa dit : chaque animal a un cri. Rosa &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me l'animal. Elle dit le cri.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le pommier du pré penche vers la clôture. Une pomme verte brille tout en haut. Des mouches tournent au-dessus de l'herbe. Ça sent le sucré et le crottin chaud. Tu vois le pommier, Mila ? Oui. Je veux le cheval. Le cheval du pré ? Lui donner une pomme. En ce moment, Mila lève le nez. La pomme du haut est trop loin. Je n'arrive pas. Elle est trop haute. Un hennissement arrive du pré. Hiii, long et doux. Le cheval ! Tu as entendu ? Il appelle. Le cheval hennit. Mila marche le long de la clôture. L'herbe racle ses mollets. Une pomme brune dort dans l'herbe. Une à terre ! On la ramasse ? Oui. Mila se baisse. La pomme est froide et un peu molle. Elle la tend vers le pré. On ne donne pas tout seuls. Je la donne, d'accord ? D'accord. Papa prend la pomme dans sa main. Le cheval s'approche de la clôture. Son museau est velours et tiède. Il souffle. Hiii. Une mouche se pose sur l'encolure. Il attend la pomme. Oui. Les naseaux du cheval s'ouvrent tout grand. La clôture tremble un peu sous le poil. Il est tout près. On reste de ce côté. Mila sent le sucré de la pomme froide.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,11 +1324,50 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Rosa marche avec papa. Ils suivent le chemin du pré. Un chien arrive. Le chien aboie. Ouaf ouaf.
-papa|Le chien aboie. C'est son cri.
-narrateur|Un chat saute près d'une botte. Le chat miaule. Miaou. Une vache mange l'herbe. La vache meugle. Meuh. Un coq est sur la clôture. Le coq chante. Cocorico. Un mouton s'approche. Le mouton bêle. Bêê. Un canard nage dans la mare. Le canard cancane.
-papa|Chaque animal a un cri.
-narrateur|Rosa nomme l'animal. Elle dit le cri.</t>
+          <t>narrateur|Le pommier du pré penche vers la clôture.
+narrateur|Une pomme verte brille tout en haut.
+narrateur|Des mouches tournent au-dessus de l'herbe.
+narrateur|Ça sent le sucré et le crottin chaud.
+papa|Tu vois le pommier, Mila ?
+enfant-f|Oui.
+enfant-f|Je veux le cheval.
+papa|Le cheval du pré ?
+enfant-f|Lui donner une pomme.
+narrateur|En ce moment, Mila lève le nez.
+narrateur|La pomme du haut est trop loin.
+enfant-f|Je n'arrive pas.
+papa|Elle est trop haute.
+narrateur|Un hennissement arrive du pré.
+narrateur|Hiii, long et doux.
+enfant-f|Le cheval !
+papa|Tu as entendu ?
+enfant-f|Il appelle.
+papa|Le cheval hennit.
+narrateur|Mila marche le long de la clôture.
+narrateur|L'herbe racle ses mollets.
+narrateur|Une pomme brune dort dans l'herbe.
+enfant-f|Une à terre !
+papa|On la ramasse ?
+enfant-f|Oui.
+narrateur|Mila se baisse.
+narrateur|La pomme est froide et un peu molle.
+narrateur|Elle la tend vers le pré.
+papa|On ne donne pas tout seuls.
+papa|Je la donne, d'accord ?
+enfant-f|D'accord.
+narrateur|Papa prend la pomme dans sa main.
+narrateur|Le cheval s'approche de la clôture.
+narrateur|Son museau est velours et tiède.
+narrateur|Il souffle.
+narrateur|Hiii.
+narrateur|Une mouche se pose sur l'encolure.
+enfant-f|Il attend la pomme.
+papa|Oui.
+narrateur|Les naseaux du cheval s'ouvrent tout grand.
+narrateur|La clôture tremble un peu sous le poil.
+enfant-f|Il est tout près.
+papa|On reste de ce côté.
+narrateur|Mila sent le sucré de la pomme froide.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,12 +1399,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le chien fait ouaf. Quel est son cri ?</t>
+          <t>Le cheval fait hiii. Quel est le cri du cheval ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le chien fait ouaf. Quel est son &lt;emphasis level="moderate"&gt;cri&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cheval fait hiii. Quel est le cri du cheval ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,12 +1414,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>aboie</t>
+          <t>hennit</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>aboie | il aboie | ouaf | le cri</t>
+          <t>hennit | il hennit | hiii | le cri | le cheval</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1434,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Le chien aboie. Quel est le cri ?</t>
+          <t>Le cheval hennit. Quel est le cri ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1432,7 +1483,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1508,7 +1559,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le chien fait ouaf. Quel est son cri ?</t>
+          <t>narrateur|Le cheval fait hiii.
+narrateur|Quel est le cri du cheval ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -1540,12 +1592,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Rosa a nommé l'animal. Elle a dit le cri. Chien, chat, vache, coq, mouton, canard.</t>
+          <t>Papa pose la pomme sur sa paume ouverte. Le cheval croque. Ça fait un bruit sec. Il mange. Merci d'avoir attendu, Mila. On donne avec un adulte. Il hennit. Oui. Hiii. Un filet de jus coule sur le poil. Mila reste derrière la clôture. Elle ne tend plus la main. On le regarde d'ici ? Oui. La queue du cheval chasse une mouche. L'herbe sent encore le sucré.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Rosa a &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;mé l'animal. Elle a dit le cri. Chien, chat, vache, coq, mouton, canard.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa pose la pomme sur sa paume ouverte. Le cheval croque. Ça fait un bruit sec. Il mange. Merci d'avoir attendu, Mila. On donne avec un adulte. Il hennit. Oui. Hiii. Un filet de jus coule sur le poil. Mila reste derrière la clôture. Elle ne tend plus la main. On le regarde d'ici ? Oui. La queue du cheval chasse une mouche. L'herbe sent encore le sucré.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1608,7 +1660,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1684,7 +1736,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Rosa a nommé l'animal. Elle a dit le cri. Chien, chat, vache, coq, mouton, canard.</t>
+          <t>narrateur|Papa pose la pomme sur sa paume ouverte.
+narrateur|Le cheval croque.
+narrateur|Ça fait un bruit sec.
+enfant-f|Il mange.
+papa|Merci d'avoir attendu, Mila.
+papa|On donne avec un adulte.
+enfant-f|Il hennit.
+papa|Oui.
+papa|Hiii.
+narrateur|Un filet de jus coule sur le poil.
+narrateur|Mila reste derrière la clôture.
+narrateur|Elle ne tend plus la main.
+papa|On le regarde d'ici ?
+enfant-f|Oui.
+narrateur|La queue du cheval chasse une mouche.
+narrateur|L'herbe sent encore le sucré.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1716,12 +1783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Rosa tient la main de papa. Le pré sent l'herbe.</t>
+          <t>La pomme a disparu d'un coup. Il reste un trognon minuscule. Il a tout pris. Tu voulais lui donner une pomme. C'est fait. Le cheval frotte le bois de la clôture. Le bois tremble un peu. Mila pose une main sur le piquet. Hiii. C'est son cri. La pomme du haut brille encore. Celle de terre a suffi. Une mouche repart vers l'herbe. Il hennit encore. Oui. Le crottin chaud sent moins, maintenant.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Rosa tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de papa. Le pré sent l'herbe.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pomme a disparu d'un coup. Il reste un trognon minuscule. Il a tout pris. Tu voulais lui donner une pomme. C'est fait. Le cheval frotte le bois de la clôture. Le bois tremble un peu. Mila pose une main sur le piquet. Hiii. C'est son cri. La pomme du haut brille encore. Celle de terre a suffi. Une mouche repart vers l'herbe. Il hennit encore. Oui. Le crottin chaud sent moins, maintenant.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1784,7 +1851,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1856,10 +1923,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Rosa tient la main de papa. Le pré sent l'herbe.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La pomme a disparu d'un coup.
+narrateur|Il reste un trognon minuscule.
+enfant-f|Il a tout pris.
+papa|Tu voulais lui donner une pomme.
+papa|C'est fait.
+narrateur|Le cheval frotte le bois de la clôture.
+narrateur|Le bois tremble un peu.
+narrateur|Mila pose une main sur le piquet.
+enfant-f|Hiii.
+papa|C'est son cri.
+narrateur|La pomme du haut brille encore.
+narrateur|Celle de terre a suffi.
+narrateur|Une mouche repart vers l'herbe.
+enfant-f|Il hennit encore.
+papa|Oui.
+narrateur|Le crottin chaud sent moins, maintenant.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1884,12 +1965,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le museau du cheval sent encore la pomme. Mila prend la main de papa. Il a mangé. Oui. Le pommier penche, tout tranquille.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le museau du cheval sent encore la pomme. Mila prend la main de papa. Il a mangé. Oui. Le pommier penche, tout tranquille.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1945,14 +2026,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2024,10 +2105,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le museau du cheval sent encore la pomme.
+narrateur|Mila prend la main de papa.
+enfant-f|Il a mangé.
+papa|Oui.
+narrateur|Le pommier penche, tout tranquille.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2046,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2084,6 +2168,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-04.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pré près de la ferme</t>
+          <t>pré près de la ferme, pommier contre la clôture</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rosa, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
